--- a/data/trans_bre/LAWTONB_2R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Edad-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-11,26%</t>
         </is>
       </c>
     </row>
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,8; 7,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,09; 6,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,79; 7,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,6; 3,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,63; 180,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-26,11; 105,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,21; 169,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,6; 50,93</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,43</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,17; 13,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,79; 12,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,14; 18,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,72; 22,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,72; 72,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,59; 44,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,81; 77,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,47; 90,06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -860,565 +860,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,36; 9,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,31; 10,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,51; 13,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,61; 12,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,57; 89,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,15; 61,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,84; 103,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,86; 80,78</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-11,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 7,59</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 6,58</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 7,2</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 3,59</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-12,46; 163,87</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-27,36; 93,64</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-7,77; 160,54</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-67,64; 53,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>5,62</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,43</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 13,01</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 13,4</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2,84; 18,23</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 22,59</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-8,91; 70,38</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-8,59; 45,01</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,44; 78,86</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36,92; 89,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5,37</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>8,5</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>44,5%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>56,44%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 9,62</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0,79; 10,99</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4,08; 13,05</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 12,72</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10,9; 91,11</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,41; 60,66</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>23,81; 101,07</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-28,72; 80,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="6">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/LAWTONB_2R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-11,26%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,54</t>
+          <t>-0,46; 7,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,79</t>
+          <t>-3,08; 6,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 7,54</t>
+          <t>-0,77; 7,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 3,45</t>
+          <t>0,17; 6,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 180,22</t>
+          <t>-7,48; 178,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 105,21</t>
+          <t>-26,16; 91,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 169,98</t>
+          <t>-8,92; 156,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 50,93</t>
+          <t>-0,38; 116,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>18,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 13,01</t>
+          <t>-2,43; 12,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 12,78</t>
+          <t>-3,15; 13,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 18,28</t>
+          <t>2,88; 17,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 22,53</t>
+          <t>12,78; 23,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 72,21</t>
+          <t>-9,83; 72,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 44,81</t>
+          <t>-7,76; 46,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 77,99</t>
+          <t>9,71; 79,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,47; 90,06</t>
+          <t>40,68; 95,39</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,7</t>
+          <t>1,27; 9,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,92</t>
+          <t>0,54; 10,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,28</t>
+          <t>4,1; 13,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 12,89</t>
+          <t>9,19; 15,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 89,44</t>
+          <t>6,46; 91,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 61,16</t>
+          <t>2,4; 57,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,84; 103,38</t>
+          <t>23,98; 99,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 80,78</t>
+          <t>49,22; 111,34</t>
         </is>
       </c>
     </row>
